--- a/data/qkumite.xlsx
+++ b/data/qkumite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ ds\MermaidApp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDCD8AF-E86C-4C02-AD89-0316534EEEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A1F7FE-59D7-4FF3-A739-48962AC9A735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/qkumite.xlsx
+++ b/data/qkumite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ Claude.ai\Quiz app\karate-tf-app\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ Claude.ai\mermaid app\App-2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64EC612-A3A2-49E3-9774-56798B3FD8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF956CB-8698-4E75-B93B-B258DF42C506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 V,2" sheetId="3" r:id="rId1"/>
@@ -3524,7 +3524,7 @@
         <v>209</v>
       </c>
       <c r="C204" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
